--- a/files/05-2619-s-sepulveda-blvd.xlsx
+++ b/files/05-2619-s-sepulveda-blvd.xlsx
@@ -8,17 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iniculete\LAAA-Deploys\onmarket\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A23533AC-1A8E-48CC-8A1F-5BC6C5112D1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{382E8485-15C7-4A59-A516-117F1199A86E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{62A88C20-60D6-4932-8D8F-82CBE5089EFC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{0FDE9C1F-490A-48EC-A8F2-D9A12440A6FD}"/>
   </bookViews>
   <sheets>
     <sheet name="Assumptions" sheetId="1" r:id="rId1"/>
     <sheet name="05 2619 S Sepulveda Blvd" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'05 2619 S Sepulveda Blvd'!$A$1:$N$78</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -43,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="144">
   <si>
     <t>LAAA UNDERWRITING BENCHMARKS (edit here; every deal tab reads these)</t>
   </si>
@@ -195,10 +192,10 @@
     <t>LoopNet listing</t>
   </si>
   <si>
-    <t>Data pulled 9/17/2026 from LoopNet public listing</t>
-  </si>
-  <si>
-    <t>NOTE: $325K reduction</t>
+    <t>Data pulled 9/17/2026 from LoopNet public listing + rent roll and expenses read from the listing broker's OM (RE/MAX Commercial &amp; Investment Realty (Taksa Investment Group), Jonathan Taksa, rent roll 7/1/2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOTE: $325K reduction | OM: Price: OM states $5,900,000 (cap 5.64%, GRM 11.19); LoopNet listing at $5,575,000 implies a price reduction after the OM date. At $5,575,000 the OM NOI gives 5.97% cap / 10.57 GRM.; Vacant unit: 2619 S Sepulveda #1 (1+1) is vacant and carried at the $1,995 asking/market rent inside the current GSR; </t>
   </si>
   <si>
     <t>PROPERTY</t>
@@ -303,13 +300,19 @@
     <t>Rent source</t>
   </si>
   <si>
-    <t>2 Bd / 2 Ba  (~975 SF)</t>
-  </si>
-  <si>
-    <t>Allocated from published GRM (price / GRM) using LAAA bed weights</t>
-  </si>
-  <si>
-    <t>1 Bd / 1 Ba  (~650 SF)</t>
+    <t>2 Bd / 2 Ba  (~975 SF)  [range $1,520-$2,600; one is the manager's unit at $1,800]</t>
+  </si>
+  <si>
+    <t>OM rent roll, current in-place rents (OM rent roll 7/1/2026)</t>
+  </si>
+  <si>
+    <t>1 Bd / 1 Ba  (~800 SF)  [range $991-$1,995; includes 1 vacant unit (2619 #1) carried ]</t>
+  </si>
+  <si>
+    <t>Studio  (~400 SF)  [studios with full kitchens; range $842-$1,650]</t>
+  </si>
+  <si>
+    <t>Bachelor  (~300 SF)  [single unit]</t>
   </si>
   <si>
     <t>Total / weighted avg</t>
@@ -330,7 +333,7 @@
     <t>Scheduled gross rent</t>
   </si>
   <si>
-    <t>OM column: price / published GRM</t>
+    <t>OM column: OM stated current scheduled rent (OM rent roll 7/1/2026); LAAA column: OM rent roll by unit type</t>
   </si>
   <si>
     <t>Other income (laundry, parking, RUBS)</t>
@@ -342,7 +345,7 @@
     <t>Vacancy &amp; credit loss</t>
   </si>
   <si>
-    <t>OM 3.0% (OM figure if extracted, else 3% assumed); LAAA per Assumptions</t>
+    <t>OM 3.0%; LAAA per Assumptions</t>
   </si>
   <si>
     <t>Effective gross income</t>
@@ -387,7 +390,7 @@
     <t>Utilities (water/sewer/trash/common electric &amp; gas)</t>
   </si>
   <si>
-    <t>per unit, by city</t>
+    <t>per unit, by city; OM utilities + water/sewer + gas/electric + trash combined</t>
   </si>
   <si>
     <t>Contract services (landscape, pest, cleaning)</t>
@@ -396,10 +399,10 @@
     <t>per unit</t>
   </si>
   <si>
-    <t>Admin / legal / licenses / rent registration</t>
-  </si>
-  <si>
-    <t>per unit; OM "other" items land here</t>
+    <t>Admin / legal / licenses / rent registration / other OM items</t>
+  </si>
+  <si>
+    <t>OM other items: Contract Services 25,000</t>
   </si>
   <si>
     <t>Replacement reserves</t>
@@ -408,7 +411,7 @@
     <t>Total operating expenses</t>
   </si>
   <si>
-    <t>OM line items not published. OM total IMPLIED = OM EGI - (price x published cap)</t>
+    <t>OM line items from OM (OM rent roll 7/1/2026); basis: OM 'Current' column of Operating Data (p.14); broker estimates 'based partly on industry standards', not owner actuals. Taxes = 1.18738% of $5.9M price. Management = Off-Site $1,800 + On-Site $9,600. Pro Forma column is identical ($181,588). Utilities is a single combined line.; OM total 181,588</t>
   </si>
   <si>
     <t>Expenses per unit</t>
@@ -424,6 +427,9 @@
   </si>
   <si>
     <t>Net operating income</t>
+  </si>
+  <si>
+    <t>OM states NOI 332,805 / cap 5.64</t>
   </si>
   <si>
     <t>Cap rate on asking price</t>
@@ -472,12 +478,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="\$#,##0;\(\$#,##0\);&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="\$#,##0.00"/>
     <numFmt numFmtId="166" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0;\(&quot;$&quot;#,##0\);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -525,6 +532,7 @@
       <sz val="11"/>
       <color rgb="FFC00000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -533,8 +541,21 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF595959"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -562,7 +583,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF9E5"/>
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -598,7 +620,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -622,12 +644,15 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -660,7 +685,7 @@
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2010B00C-CFB1-4744-83DC-372CB02A3ACB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B0C4BBA0-CB11-4305-96EF-E139ED9E47AE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -971,7 +996,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21C7501B-C0A6-4B5E-9FEA-0B2B035225FB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C27CC0F-B7A2-4046-8579-30C947D4627A}">
   <dimension ref="A1:C40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1340,11 +1365,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8885E609-1E04-4E71-8666-A00DF879D807}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BEA8005-72CD-4527-B2EC-3E69B9E0CD7B}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:F76"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -1574,17 +1599,17 @@
         <v>3</v>
       </c>
       <c r="C30" s="21">
-        <v>2282</v>
-      </c>
-      <c r="D30" s="8">
+        <v>1973</v>
+      </c>
+      <c r="D30" s="22">
         <f>B30*C30</f>
-        <v>6846</v>
-      </c>
-      <c r="E30" s="8">
+        <v>5919</v>
+      </c>
+      <c r="E30" s="22">
         <f>D30*12</f>
-        <v>82152</v>
-      </c>
-      <c r="F30" s="2" t="s">
+        <v>71028</v>
+      </c>
+      <c r="F30" s="23" t="s">
         <v>87</v>
       </c>
     </row>
@@ -1596,99 +1621,106 @@
         <v>13</v>
       </c>
       <c r="C31" s="21">
-        <v>1690</v>
-      </c>
-      <c r="D31" s="8">
+        <v>1596</v>
+      </c>
+      <c r="D31" s="22">
         <f>B31*C31</f>
-        <v>21970</v>
-      </c>
-      <c r="E31" s="8">
+        <v>20748</v>
+      </c>
+      <c r="E31" s="22">
         <f>D31*12</f>
-        <v>263640</v>
-      </c>
-      <c r="F31" s="2" t="s">
+        <v>248976</v>
+      </c>
+      <c r="F31" s="23" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>34</v>
+        <v>89</v>
       </c>
       <c r="B32" s="15">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C32" s="21">
-        <v>1183</v>
-      </c>
-      <c r="D32" s="8">
+        <v>1347</v>
+      </c>
+      <c r="D32" s="22">
         <f>B32*C32</f>
-        <v>15379</v>
-      </c>
-      <c r="E32" s="8">
+        <v>16164</v>
+      </c>
+      <c r="E32" s="22">
         <f>D32*12</f>
-        <v>184548</v>
-      </c>
-      <c r="F32" s="2" t="s">
+        <v>193968</v>
+      </c>
+      <c r="F32" s="23" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="B33" s="23">
-        <f>SUM(B30:B32)</f>
+      <c r="A33" t="s">
+        <v>90</v>
+      </c>
+      <c r="B33" s="15">
+        <v>1</v>
+      </c>
+      <c r="C33" s="21">
+        <v>1100</v>
+      </c>
+      <c r="D33" s="22">
+        <f>B33*C33</f>
+        <v>1100</v>
+      </c>
+      <c r="E33" s="22">
+        <f>D33*12</f>
+        <v>13200</v>
+      </c>
+      <c r="F33" s="23" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="B34" s="25">
+        <f>SUM(B30:B33)</f>
         <v>29</v>
       </c>
-      <c r="C33" s="24">
-        <f>IFERROR(D33/B33,"")</f>
-        <v>1523.9655172413793</v>
-      </c>
-      <c r="D33" s="24">
-        <f>SUM(D30:D32)</f>
-        <v>44195</v>
-      </c>
-      <c r="E33" s="24">
-        <f>SUM(E30:E32)</f>
-        <v>530340</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
+      <c r="C34" s="26">
+        <f>IFERROR(D34/B34,"")</f>
+        <v>1514.8620689655172</v>
+      </c>
+      <c r="D34" s="26">
+        <f>SUM(D30:D33)</f>
+        <v>43931</v>
+      </c>
+      <c r="E34" s="26">
+        <f>SUM(E30:E33)</f>
+        <v>527172</v>
+      </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="25"/>
-      <c r="B36" s="25" t="s">
-        <v>91</v>
-      </c>
-      <c r="C36" s="25" t="s">
+      <c r="A36" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="D36" s="25"/>
-      <c r="E36" s="25"/>
-      <c r="F36" s="25" t="s">
+      <c r="B36" s="14"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="27"/>
+      <c r="B37" s="27" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+      <c r="C37" s="27" t="s">
         <v>94</v>
       </c>
-      <c r="B37" s="8">
-        <v>530447.19314938155</v>
-      </c>
-      <c r="C37" s="8">
-        <f>E33</f>
-        <v>530340</v>
-      </c>
-      <c r="F37" s="2" t="s">
+      <c r="D37" s="27"/>
+      <c r="E37" s="27"/>
+      <c r="F37" s="27" t="s">
         <v>95</v>
       </c>
     </row>
@@ -1696,122 +1728,118 @@
       <c r="A38" t="s">
         <v>96</v>
       </c>
-      <c r="B38" s="8">
-        <v>0</v>
-      </c>
-      <c r="C38" s="4">
-        <v>0</v>
+      <c r="B38" s="22">
+        <v>527209</v>
+      </c>
+      <c r="C38" s="8">
+        <f>E34</f>
+        <v>527172</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="22" t="s">
-        <v>97</v>
+      <c r="A39" t="s">
+        <v>98</v>
       </c>
       <c r="B39" s="8">
-        <f>B37+B38</f>
-        <v>530447.19314938155</v>
-      </c>
-      <c r="C39" s="8">
-        <f>C37+C38</f>
-        <v>530340</v>
+        <v>3000</v>
+      </c>
+      <c r="C39" s="4">
+        <v>3000</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>98</v>
+      <c r="A40" s="24" t="s">
+        <v>99</v>
       </c>
       <c r="B40" s="8">
-        <f>-B37*0.03</f>
-        <v>-15913.415794481445</v>
+        <f>B38+B39</f>
+        <v>530209</v>
       </c>
       <c r="C40" s="8">
-        <f>-C37*Assumptions!$B$3</f>
-        <v>-15910.199999999999</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>99</v>
+        <f>C38+C39</f>
+        <v>530172</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="22" t="s">
+      <c r="A41" t="s">
         <v>100</v>
       </c>
-      <c r="B41" s="24">
-        <f>B39+B40</f>
-        <v>514533.77735490008</v>
-      </c>
-      <c r="C41" s="24">
-        <f>C39+C40</f>
-        <v>514429.8</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="13" t="s">
+      <c r="B41" s="8">
+        <f>-B38*0.03</f>
+        <v>-15816.269999999999</v>
+      </c>
+      <c r="C41" s="8">
+        <f>-C38*Assumptions!$B$3</f>
+        <v>-15815.16</v>
+      </c>
+      <c r="F41" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="B42" s="26">
+        <f>B40+B41</f>
+        <v>514392.73</v>
+      </c>
+      <c r="C42" s="26">
+        <f>C40+C41</f>
+        <v>514356.84</v>
+      </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="25" t="s">
-        <v>102</v>
-      </c>
-      <c r="B44" s="25" t="s">
-        <v>91</v>
-      </c>
-      <c r="C44" s="25" t="s">
+      <c r="A44" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="D44" s="25" t="s">
-        <v>92</v>
-      </c>
-      <c r="E44" s="25" t="s">
+      <c r="B44" s="14"/>
+      <c r="C44" s="14"/>
+      <c r="D44" s="14"/>
+      <c r="E44" s="14"/>
+      <c r="F44" s="14"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="27" t="s">
         <v>104</v>
       </c>
-      <c r="F44" s="25" t="s">
+      <c r="B45" s="27" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+      <c r="C45" s="27" t="s">
         <v>105</v>
       </c>
-      <c r="B45" s="8"/>
-      <c r="C45" s="8">
-        <f>B22*Assumptions!$B$15</f>
-        <v>69687.5</v>
-      </c>
-      <c r="D45" s="26">
-        <f>C45</f>
-        <v>69687.5</v>
-      </c>
-      <c r="E45" s="8" t="str">
-        <f t="shared" ref="E45:E53" si="0">IF(ISNUMBER(B45),D45-B45,"")</f>
-        <v/>
-      </c>
-      <c r="F45" s="2" t="s">
+      <c r="D45" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="E45" s="27" t="s">
         <v>106</v>
+      </c>
+      <c r="F45" s="27" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>107</v>
       </c>
-      <c r="B46" s="8"/>
+      <c r="B46" s="22">
+        <v>70055</v>
+      </c>
       <c r="C46" s="8">
-        <f>B7*Assumptions!$B$5+B8*Assumptions!$B$6</f>
-        <v>24916</v>
-      </c>
-      <c r="D46" s="26">
-        <f t="shared" ref="D46:D52" si="1">IF(ISNUMBER(B46),MAX(B46,C46),C46)</f>
-        <v>24916</v>
-      </c>
-      <c r="E46" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+        <f>B22*Assumptions!$B$15</f>
+        <v>69687.5</v>
+      </c>
+      <c r="D46" s="28">
+        <f>C46</f>
+        <v>69687.5</v>
+      </c>
+      <c r="E46" s="8">
+        <f t="shared" ref="E46:E54" si="0">IF(ISNUMBER(B46),D46-B46,"")</f>
+        <v>-367.5</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>108</v>
@@ -1821,18 +1849,20 @@
       <c r="A47" t="s">
         <v>109</v>
       </c>
-      <c r="B47" s="8"/>
+      <c r="B47" s="22">
+        <v>17133</v>
+      </c>
       <c r="C47" s="8">
-        <f>C41*Assumptions!$B$4</f>
-        <v>25721.49</v>
-      </c>
-      <c r="D47" s="26">
-        <f t="shared" si="1"/>
-        <v>25721.49</v>
-      </c>
-      <c r="E47" s="8" t="str">
+        <f>B7*Assumptions!$B$5+B8*Assumptions!$B$6</f>
+        <v>24916</v>
+      </c>
+      <c r="D47" s="28">
+        <f t="shared" ref="D47:D53" si="1">IF(ISNUMBER(B47),MAX(B47,C47),C47)</f>
+        <v>24916</v>
+      </c>
+      <c r="E47" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>7783</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>110</v>
@@ -1842,18 +1872,20 @@
       <c r="A48" t="s">
         <v>111</v>
       </c>
-      <c r="B48" s="8"/>
+      <c r="B48" s="22">
+        <v>11400</v>
+      </c>
       <c r="C48" s="8">
-        <f>B7*Assumptions!$B$7</f>
-        <v>34800</v>
-      </c>
-      <c r="D48" s="26">
+        <f>C42*Assumptions!$B$4</f>
+        <v>25717.842000000004</v>
+      </c>
+      <c r="D48" s="28">
         <f t="shared" si="1"/>
-        <v>34800</v>
-      </c>
-      <c r="E48" s="8" t="str">
+        <v>25717.842000000004</v>
+      </c>
+      <c r="E48" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>14317.842000000004</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>112</v>
@@ -1863,18 +1895,20 @@
       <c r="A49" t="s">
         <v>113</v>
       </c>
-      <c r="B49" s="8"/>
+      <c r="B49" s="22">
+        <v>29000</v>
+      </c>
       <c r="C49" s="8">
-        <f>B7*Assumptions!$B$9</f>
-        <v>43500</v>
-      </c>
-      <c r="D49" s="26">
+        <f>B7*Assumptions!$B$7</f>
+        <v>34800</v>
+      </c>
+      <c r="D49" s="28">
         <f t="shared" si="1"/>
-        <v>43500</v>
-      </c>
-      <c r="E49" s="8" t="str">
+        <v>34800</v>
+      </c>
+      <c r="E49" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>5800</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>114</v>
@@ -1884,18 +1918,20 @@
       <c r="A50" t="s">
         <v>115</v>
       </c>
-      <c r="B50" s="8"/>
+      <c r="B50" s="22">
+        <v>29000</v>
+      </c>
       <c r="C50" s="8">
-        <f>B7*Assumptions!$B$12</f>
-        <v>11600</v>
-      </c>
-      <c r="D50" s="26">
+        <f>B7*Assumptions!$B$9</f>
+        <v>43500</v>
+      </c>
+      <c r="D50" s="28">
         <f t="shared" si="1"/>
-        <v>11600</v>
-      </c>
-      <c r="E50" s="8" t="str">
+        <v>43500</v>
+      </c>
+      <c r="E50" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>14500</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>116</v>
@@ -1905,14 +1941,14 @@
       <c r="A51" t="s">
         <v>117</v>
       </c>
-      <c r="B51" s="8"/>
+      <c r="B51" s="22"/>
       <c r="C51" s="8">
-        <f>B7*Assumptions!$B$13</f>
-        <v>7250</v>
-      </c>
-      <c r="D51" s="26">
+        <f>B7*Assumptions!$B$12</f>
+        <v>11600</v>
+      </c>
+      <c r="D51" s="28">
         <f t="shared" si="1"/>
-        <v>7250</v>
+        <v>11600</v>
       </c>
       <c r="E51" s="8" t="str">
         <f t="shared" si="0"/>
@@ -1926,263 +1962,288 @@
       <c r="A52" t="s">
         <v>119</v>
       </c>
-      <c r="B52" s="8"/>
+      <c r="B52" s="22">
+        <v>25000</v>
+      </c>
       <c r="C52" s="8">
+        <f>B7*Assumptions!$B$13</f>
+        <v>7250</v>
+      </c>
+      <c r="D52" s="28">
+        <f t="shared" si="1"/>
+        <v>25000</v>
+      </c>
+      <c r="E52" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>121</v>
+      </c>
+      <c r="B53" s="22"/>
+      <c r="C53" s="8">
         <f>B7*Assumptions!$B$14</f>
         <v>8700</v>
       </c>
-      <c r="D52" s="26">
+      <c r="D53" s="28">
         <f t="shared" si="1"/>
         <v>8700</v>
       </c>
-      <c r="E52" s="8" t="str">
+      <c r="E53" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="F52" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="22" t="s">
-        <v>120</v>
-      </c>
-      <c r="B53" s="24">
-        <f>B41-B22*B25</f>
-        <v>184493.77735490008</v>
-      </c>
-      <c r="C53" s="24">
-        <f>SUM(C45:C52)</f>
-        <v>226174.99</v>
-      </c>
-      <c r="D53" s="24">
-        <f>SUM(D45:D52)</f>
-        <v>226174.99</v>
-      </c>
-      <c r="E53" s="24">
+      <c r="F53" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="24" t="s">
+        <v>122</v>
+      </c>
+      <c r="B54" s="26">
+        <f>SUM(B46:B53)</f>
+        <v>181588</v>
+      </c>
+      <c r="C54" s="26">
+        <f>SUM(C46:C53)</f>
+        <v>226171.342</v>
+      </c>
+      <c r="D54" s="26">
+        <f>SUM(D46:D53)</f>
+        <v>243921.342</v>
+      </c>
+      <c r="E54" s="26">
         <f t="shared" si="0"/>
-        <v>41681.212645099906</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>122</v>
-      </c>
-      <c r="B54" s="8">
-        <f>IFERROR(B53/B7,"")</f>
-        <v>6361.8543915482787</v>
-      </c>
-      <c r="C54" s="8">
-        <f>IFERROR(C53/B7,"")</f>
-        <v>7799.1375862068962</v>
-      </c>
-      <c r="D54" s="8">
-        <f>IFERROR(D53/B7,"")</f>
-        <v>7799.1375862068962</v>
+        <v>62333.342000000004</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>123</v>
-      </c>
-      <c r="B55" s="18">
-        <f>IFERROR(B53/B41,"")</f>
-        <v>0.35856494845360826</v>
-      </c>
-      <c r="C55" s="18">
-        <f>IFERROR(C53/C41,"")</f>
-        <v>0.4396615242740603</v>
-      </c>
-      <c r="D55" s="18">
-        <f>IF(C37&gt;0,IFERROR(D53/C41,""),"")</f>
-        <v>0.4396615242740603</v>
+        <v>124</v>
+      </c>
+      <c r="B55" s="8">
+        <f>IFERROR(B54/B7,"")</f>
+        <v>6261.6551724137935</v>
+      </c>
+      <c r="C55" s="8">
+        <f>IFERROR(C54/B7,"")</f>
+        <v>7799.0117931034483</v>
+      </c>
+      <c r="D55" s="8">
+        <f>IFERROR(D54/B7,"")</f>
+        <v>8411.0807586206902</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="22" t="s">
-        <v>124</v>
-      </c>
-      <c r="B56" s="12" t="str">
-        <f>IF(ISNUMBER(B53),IF(D53&gt;B53*(1+Assumptions!$B$24),"OM EXPENSES LIGHT","OM expenses reasonable"),"OM expenses not published")</f>
+      <c r="A56" t="s">
+        <v>125</v>
+      </c>
+      <c r="B56" s="18">
+        <f>IFERROR(B54/B42,"")</f>
+        <v>0.35301432040067909</v>
+      </c>
+      <c r="C56" s="18">
+        <f>IFERROR(C54/C42,"")</f>
+        <v>0.43971679661147306</v>
+      </c>
+      <c r="D56" s="18">
+        <f>IF(C38&gt;0,IFERROR(D54/C42,""),"")</f>
+        <v>0.47422591288958071</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="B57" s="29" t="str">
+        <f>IF(ISNUMBER(B54),IF(D54&gt;B54*(1+Assumptions!$B$24),"OM EXPENSES LIGHT","OM expenses reasonable"),"OM expenses not published")</f>
         <v>OM EXPENSES LIGHT</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="B58" s="14"/>
-      <c r="C58" s="14"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="14"/>
-      <c r="F58" s="14"/>
-    </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="25"/>
-      <c r="B59" s="25" t="s">
-        <v>91</v>
-      </c>
-      <c r="C59" s="25" t="s">
-        <v>92</v>
-      </c>
-      <c r="D59" s="25"/>
-      <c r="E59" s="25"/>
-      <c r="F59" s="25" t="s">
+      <c r="A59" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="B59" s="14"/>
+      <c r="C59" s="14"/>
+      <c r="D59" s="14"/>
+      <c r="E59" s="14"/>
+      <c r="F59" s="14"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="27"/>
+      <c r="B60" s="27" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="B60" s="24">
-        <f>B41-B53</f>
-        <v>330040</v>
-      </c>
-      <c r="C60" s="24">
-        <f>IF(C37&gt;0,C41-D53,"")</f>
-        <v>288254.81</v>
+      <c r="C60" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="D60" s="27"/>
+      <c r="E60" s="27"/>
+      <c r="F60" s="27" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="B61" s="18">
-        <f>IFERROR(B60/B22,"")</f>
-        <v>5.9200000000000003E-2</v>
-      </c>
-      <c r="C61" s="18">
-        <f>IF(C60="","",IFERROR(C60/B22,""))</f>
-        <v>5.1704898654708523E-2</v>
-      </c>
-      <c r="F61" s="2" t="s">
+      <c r="A61" s="24" t="s">
         <v>128</v>
       </c>
+      <c r="B61" s="26">
+        <f>B42-B54</f>
+        <v>332804.73</v>
+      </c>
+      <c r="C61" s="26">
+        <f>IF(C38&gt;0,C42-D54,"")</f>
+        <v>270435.49800000002</v>
+      </c>
+      <c r="F61" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>129</v>
-      </c>
-      <c r="B62" s="19">
-        <f>IFERROR(B22/B37,"")</f>
-        <v>10.51</v>
-      </c>
-      <c r="C62" s="19">
-        <f>IF(C37&gt;0,IFERROR(B22/C37,""),"")</f>
-        <v>10.512124297620394</v>
+      <c r="A62" s="24" t="s">
+        <v>130</v>
+      </c>
+      <c r="B62" s="18">
+        <f>IFERROR(B61/B22,"")</f>
+        <v>5.9695915695067263E-2</v>
+      </c>
+      <c r="C62" s="18">
+        <f>IF(C61="","",IFERROR(C61/B22,""))</f>
+        <v>4.8508609506726461E-2</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>130</v>
-      </c>
-      <c r="B63" s="8">
-        <f>IFERROR(B60/B7,"")</f>
-        <v>11380.689655172413</v>
-      </c>
-      <c r="C63" s="8">
-        <f>IF(C60="","",IFERROR(C60/B7,""))</f>
-        <v>9939.8210344827585</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="B65" s="14"/>
-      <c r="C65" s="14"/>
-      <c r="D65" s="14"/>
-      <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
+        <v>132</v>
+      </c>
+      <c r="B63" s="19">
+        <f>IFERROR(B22/B38,"")</f>
+        <v>10.574553924534673</v>
+      </c>
+      <c r="C63" s="19">
+        <f>IF(C38&gt;0,IFERROR(B22/C38,""),"")</f>
+        <v>10.575296108291033</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>133</v>
+      </c>
+      <c r="B64" s="8">
+        <f>IFERROR(B61/B7,"")</f>
+        <v>11476.025172413792</v>
+      </c>
+      <c r="C64" s="8">
+        <f>IF(C61="","",IFERROR(C61/B7,""))</f>
+        <v>9325.362000000001</v>
+      </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>132</v>
-      </c>
-      <c r="B66" s="8">
+      <c r="A66" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="B66" s="14"/>
+      <c r="C66" s="14"/>
+      <c r="D66" s="14"/>
+      <c r="E66" s="14"/>
+      <c r="F66" s="14"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>135</v>
+      </c>
+      <c r="B67" s="8">
         <f>IFERROR(B22*Assumptions!$B$20,"")</f>
         <v>3345000</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>133</v>
-      </c>
-      <c r="B67" s="8">
-        <f>IF(C60="","",IFERROR(PV(Assumptions!$B$22/12,Assumptions!$B$23*12,-C60/Assumptions!$B$21/12),""))</f>
-        <v>3121073.655247129</v>
-      </c>
-    </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="22" t="s">
-        <v>134</v>
+      <c r="A68" t="s">
+        <v>136</v>
       </c>
       <c r="B68" s="8">
-        <f>IFERROR(MIN(B66,B67),"")</f>
-        <v>3121073.655247129</v>
+        <f>IF(C61="","",IFERROR(PV(Assumptions!$B$22/12,Assumptions!$B$23*12,-C61/Assumptions!$B$21/12),""))</f>
+        <v>2928135.3822038136</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>135</v>
+      <c r="A69" s="24" t="s">
+        <v>137</v>
       </c>
       <c r="B69" s="8">
-        <f>IFERROR(B22-B68,"")</f>
-        <v>2453926.344752871</v>
+        <f>IFERROR(MIN(B67,B68),"")</f>
+        <v>2928135.3822038136</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B70" s="8">
-        <f>IFERROR(-PMT(Assumptions!$B$22/12,Assumptions!$B$23*12,B68)*12,"")</f>
-        <v>230603.84799999927</v>
+        <f>IFERROR(B22-B69,"")</f>
+        <v>2646864.6177961864</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>137</v>
-      </c>
-      <c r="B71" s="19">
-        <f>IFERROR(C60/B70,"")</f>
-        <v>1.250000000000004</v>
+        <v>139</v>
+      </c>
+      <c r="B71" s="8">
+        <f>IFERROR(-PMT(Assumptions!$B$22/12,Assumptions!$B$23*12,B69)*12,"")</f>
+        <v>216348.39839999928</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>138</v>
-      </c>
-      <c r="B72" s="8">
-        <f>IFERROR(C60-B70,"")</f>
-        <v>57650.962000000727</v>
+        <v>140</v>
+      </c>
+      <c r="B72" s="19">
+        <f>IFERROR(C61/B71,"")</f>
+        <v>1.2500000000000042</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>139</v>
-      </c>
-      <c r="B73" s="18">
-        <f>IFERROR(B72/B69,"")</f>
-        <v>2.3493354689831415E-2</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
+      </c>
+      <c r="B73" s="8">
+        <f>IFERROR(C61-B71,"")</f>
+        <v>54087.099600000744</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>142</v>
+      </c>
+      <c r="B74" s="18">
+        <f>IFERROR(B73/B70,"")</f>
+        <v>2.0434403496252241E-2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
+        <v>143</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A3" r:id="rId1" xr:uid="{F49CD9B0-61B1-42B5-BE41-3F7F2D3D4E21}"/>
+    <hyperlink ref="A3" r:id="rId1" xr:uid="{F31587AD-F188-41FF-AF3A-7081AB179A9C}"/>
   </hyperlinks>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.5" footer="0.5"/>
-  <pageSetup scale="50" orientation="landscape" r:id="rId2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" r:id="rId2"/>
   <drawing r:id="rId3"/>
 </worksheet>
 </file>